--- a/seed/과제_활용데이터.xlsx
+++ b/seed/과제_활용데이터.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>영수증 정리·옮겨 적기, 합계 대조, 중복·한도 확인</t>
+          <t>영수증·자료 모으기, 정리해서 첨부하기</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>양식 항목 채우기, 메모 내용 옮기기</t>
+          <t>양식 항목 채우기, 영수증·메모 값을 양식에 옮겨 적기, 합계 맞추기</t>
         </is>
       </c>
     </row>
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G10" s="11" t="n">
         <v>1.5</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>1.4</v>
       </c>
     </row>
     <row r="11">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>영수증 정리·옮겨 적기, 합계 대조, 중복·한도 확인</t>
+          <t>영수증·자료 모으기, 정리해서 첨부하기</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>양식 항목 채우기, 메모 내용 옮기기</t>
+          <t>양식 항목 채우기, 영수증·메모 값을 양식에 옮겨 적기, 합계 맞추기</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>반려 후 재작성</t>
+          <t>진행 확인·문의</t>
         </is>
       </c>
       <c r="F4" s="19" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H4" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>증빙 준비</t>
+          <t>문서 작성</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
+          <t>진행 확인·문의</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
           <t>반려 후 재작성</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>문서 작성</t>
         </is>
       </c>
       <c r="G6" s="20" t="n">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>양식 항목이 많고 합계 맞추기가 번거로움</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>영수증 분실·흐림</t>
+          <t>첨부 형식 맞추기</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="H11" s="19" t="inlineStr">
         <is>
-          <t>영수증 하나하나 옮겨 적기</t>
+          <t>영수증 모으고 정리하기 번거로움</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H15" s="19" t="inlineStr">
         <is>
-          <t>영수증 분실·흐림</t>
+          <t>첨부 형식 맞추기</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>영수증 분실·흐림</t>
+          <t>첨부 형식 맞추기</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
+          <t>문서 작성</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
           <t>증빙 준비</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>문서 작성</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="H17" s="19" t="inlineStr">
         <is>
-          <t>영수증 분실·흐림</t>
+          <t>양식 항목이 많고 합계 맞추기가 번거로움</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>연구2팀</t>
+          <t>연구1팀</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
@@ -2544,25 +2544,25 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
+          <t>반려 후 재작성</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
           <t>증빙 준비</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>결재 검토</t>
-        </is>
-      </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>반려 후 재작성</t>
+          <t>진행 확인·문의</t>
         </is>
       </c>
       <c r="G18" s="20" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>반려 사유를 늦게 알게 됨</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="H21" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>영수증 분실·흐림</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>영수증 하나하나 옮겨 적기</t>
+          <t>영수증 모으고 정리하기 번거로움</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>영수증 분실·흐림</t>
+          <t>첨부 형식 맞추기</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>영수증 하나하나 옮겨 적기</t>
+          <t>영수증 모으고 정리하기 번거로움</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>영수증 하나하나 옮겨 적기</t>
+          <t>영수증 모으고 정리하기 번거로움</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="H29" s="19" t="inlineStr">
         <is>
-          <t>메모를 다시 옮겨 써야 함</t>
+          <t>양식 항목이 많고 합계 맞추기가 번거로움</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>영수증 분실·흐림</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>증빙 준비</t>
+          <t>처리 파악</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="H33" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>반려 후 재작성</t>
+          <t>문서 작성</t>
         </is>
       </c>
       <c r="G35" s="20" t="n">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="H37" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="H40" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H41" s="19" t="inlineStr">
         <is>
-          <t>메모를 다시 옮겨 써야 함</t>
+          <t>양식 항목이 많고 합계 맞추기가 번거로움</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>처리 파악</t>
+          <t>문서 작성</t>
         </is>
       </c>
       <c r="G42" s="20" t="n">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H44" s="19" t="inlineStr">
         <is>
-          <t>영수증 하나하나 옮겨 적기</t>
+          <t>영수증 모으고 정리하기 번거로움</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F45" s="19" t="inlineStr">
         <is>
-          <t>기타 사무</t>
+          <t>결재 검토</t>
         </is>
       </c>
       <c r="G45" s="20" t="n">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H45" s="19" t="inlineStr">
         <is>
-          <t>영수증 분실·흐림</t>
+          <t>첨부 형식 맞추기</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
-          <t>진행 확인·문의</t>
+          <t>문서 작성</t>
         </is>
       </c>
       <c r="G46" s="20" t="n">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="H46" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>영수증 분실·흐림</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="H49" s="19" t="inlineStr">
         <is>
-          <t>영수증 분실·흐림</t>
+          <t>첨부 형식 맞추기</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="H50" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>증빙 준비</t>
+          <t>문서 작성</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="H51" s="19" t="inlineStr">
         <is>
-          <t>영수증 하나하나 옮겨 적기</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
+          <t>결재 검토</t>
+        </is>
+      </c>
+      <c r="F55" s="19" t="inlineStr">
+        <is>
           <t>진행 확인·문의</t>
-        </is>
-      </c>
-      <c r="F55" s="19" t="inlineStr">
-        <is>
-          <t>반려 후 재작성</t>
         </is>
       </c>
       <c r="G55" s="20" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="H55" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="H59" s="19" t="inlineStr">
         <is>
-          <t>메모를 다시 옮겨 써야 함</t>
+          <t>양식 항목이 많고 합계 맞추기가 번거로움</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="H61" s="19" t="inlineStr">
         <is>
-          <t>영수증 분실·흐림</t>
+          <t>첨부 형식 맞추기</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>처리 파악</t>
+          <t>문서 작성</t>
         </is>
       </c>
       <c r="F63" s="19" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="H63" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>영수증 분실·흐림</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H66" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>영수증 분실·흐림</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="H67" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>영수증 분실·흐림</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="H68" s="19" t="inlineStr">
         <is>
-          <t>영수증 하나하나 옮겨 적기</t>
+          <t>영수증 모으고 정리하기 번거로움</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="H72" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H73" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>영수증 분실·흐림</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="H74" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="F80" s="19" t="inlineStr">
         <is>
-          <t>증빙 준비</t>
+          <t>반려 후 재작성</t>
         </is>
       </c>
       <c r="G80" s="20" t="n">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="H83" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H84" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H85" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>증빙 준비</t>
+          <t>문서 작성</t>
         </is>
       </c>
       <c r="F87" s="19" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="H91" s="19" t="inlineStr">
         <is>
-          <t>메모를 다시 옮겨 써야 함</t>
+          <t>양식 항목이 많고 합계 맞추기가 번거로움</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="H96" s="19" t="inlineStr">
         <is>
-          <t>메모를 다시 옮겨 써야 함</t>
+          <t>양식 항목이 많고 합계 맞추기가 번거로움</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="H97" s="19" t="inlineStr">
         <is>
-          <t>메모를 다시 옮겨 써야 함</t>
+          <t>양식 항목이 많고 합계 맞추기가 번거로움</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="E100" s="19" t="inlineStr">
         <is>
-          <t>증빙 준비</t>
+          <t>문서 작성</t>
         </is>
       </c>
       <c r="F100" s="19" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="H101" s="19" t="inlineStr">
         <is>
-          <t>영수증 분실·흐림</t>
+          <t>첨부 형식 맞추기</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E102" s="19" t="inlineStr">
         <is>
-          <t>반려 후 재작성</t>
+          <t>문서 작성</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="H102" s="19" t="inlineStr">
         <is>
-          <t>영수증 하나하나 옮겨 적기</t>
+          <t>영수증 모으고 정리하기 번거로움</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="H103" s="19" t="inlineStr">
         <is>
-          <t>영수증 하나하나 옮겨 적기</t>
+          <t>영수증 모으고 정리하기 번거로움</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="E104" s="19" t="inlineStr">
         <is>
-          <t>반려 후 재작성</t>
+          <t>문서 작성</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="H104" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>영수증 분실·흐림</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="H106" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t>진행 확인·문의</t>
+          <t>반려 후 재작성</t>
         </is>
       </c>
       <c r="F107" s="19" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="H107" s="19" t="inlineStr">
         <is>
-          <t>합계 맞추기가 번거로움</t>
+          <t>영수증 분실·흐림</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t>반려 후 재작성</t>
+          <t>진행 확인·문의</t>
         </is>
       </c>
       <c r="F117" s="19" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="H117" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="H118" s="19" t="inlineStr">
         <is>
-          <t>양식 항목이 많음</t>
+          <t>영수증 값을 양식에 하나하나 옮겨 적기</t>
         </is>
       </c>
     </row>
